--- a/download/DrMelaxin-Sheet.xlsx
+++ b/download/DrMelaxin-Sheet.xlsx
@@ -7,13 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orders" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statistics" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Orders'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Orders'!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,24 +34,73 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="24"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="008B1538"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="001C1815"/>
+      <b val="1"/>
+      <color rgb="008B1538"/>
+      <sz val="28"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="006B6358"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00D4AF37"/>
+      <sz val="28"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00016630"/>
+      <sz val="28"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="002F7D5B"/>
+      <sz val="28"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="006B6358"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="001C1815"/>
-      <sz val="14"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="008b1538"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -60,32 +109,23 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="008b1538"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="006B6358"/>
+      <color rgb="00999999"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="009A7E3A"/>
+      <color rgb="00D4AF37"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001C1815"/>
+      <color rgb="008B1538"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -94,42 +134,62 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002A2520"/>
+        <fgColor rgb="008B1538"/>
+        <bgColor rgb="008B1538"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAF8F4"/>
+        <fgColor rgb="00F7F5F2"/>
+        <bgColor rgb="00F7F5F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4AF37"/>
+        <bgColor rgb="00D4AF37"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00016630"/>
+        <bgColor rgb="00016630"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F7D5B"/>
+        <bgColor rgb="002F7D5B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002A2520"/>
+        <bgColor rgb="002A2520"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003080FF"/>
+        <bgColor rgb="003080FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD700"/>
+        <bgColor rgb="00FFD700"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E40014"/>
+        <bgColor rgb="00E40014"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="003080FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00016630"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFD700"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002F7D5B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E40014"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -143,56 +203,93 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D5CFC0"/>
+        <color rgb="00D0D0D0"/>
       </left>
       <right style="thin">
-        <color rgb="00D5CFC0"/>
+        <color rgb="00D0D0D0"/>
       </right>
       <top style="thin">
-        <color rgb="00D5CFC0"/>
+        <color rgb="00D0D0D0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D5CFC0"/>
+        <color rgb="00D0D0D0"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -200,56 +297,71 @@
   <dxfs count="5">
     <dxf>
       <font>
+        <name val="Arial"/>
         <b val="1"/>
         <color rgb="00FFFFFF"/>
+        <sz val="11"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="003080FF"/>
+          <bgColor rgb="003080FF"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <name val="Arial"/>
         <b val="1"/>
         <color rgb="00FFFFFF"/>
+        <sz val="11"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00016630"/>
+          <bgColor rgb="00016630"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <name val="Arial"/>
         <b val="1"/>
         <color rgb="001C1815"/>
+        <sz val="11"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FFD700"/>
+          <bgColor rgb="00FFD700"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <name val="Arial"/>
         <b val="1"/>
         <color rgb="00FFFFFF"/>
+        <sz val="11"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="002F7D5B"/>
+          <bgColor rgb="002F7D5B"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <name val="Arial"/>
         <b val="1"/>
         <color rgb="00FFFFFF"/>
+        <sz val="11"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00E40014"/>
+          <bgColor rgb="00E40014"/>
         </patternFill>
       </fill>
     </dxf>
@@ -615,178 +727,495 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>brandName</t>
-        </is>
-      </c>
+      <c r="A1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="50" customHeight="1">
+      <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Dr.Melaxin</t>
-        </is>
-      </c>
+          <t>لوحة التحكم · Dashboard</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>lineName</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Cemenrete CX</t>
-        </is>
-      </c>
+      <c r="A3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Calcium Volume Multi Balm</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>basePrice</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>3900</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>oldPrice</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>5800</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>taglineArabic</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>✨ ستيك للعناية بالتجاعيد لبشرة أكثر نعومة وتماسكاً.</t>
-        </is>
-      </c>
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>📊 النظرة العامة · Overview</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>إجمالي الطلبات</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي الإيرادات</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>متوسط الطلب</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>المخزون الحالي</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="n"/>
+    </row>
+    <row r="6" ht="50" customHeight="1">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="8">
+        <f>COUNTA(Orders!B2:B)</f>
+        <v/>
+      </c>
+      <c r="C6" s="9">
+        <f>SUM(Orders!I2:I)</f>
+        <v/>
+      </c>
+      <c r="D6" s="10">
+        <f>IFERROR(ROUND(AVERAGE(Orders!I2:I),0),0)</f>
+        <v/>
+      </c>
+      <c r="E6" s="11">
+        <f>Stock!B2</f>
+        <v/>
+      </c>
+      <c r="F6" s="1" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Total Orders</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Revenue (DA)</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Avg Order (DA)</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Current Stock</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>descriptionArabic</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>تساعد تركيبته على تقليل مظهر التجاعيد والخطوط الدقيقة، مع ترطيب البشرة ومنحها مظهراً أكثر إشراقاً ونعومة.</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
+      <c r="F8" s="1" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>benefitsArabic</t>
-        </is>
-      </c>
+      <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>مضاد للتجاعيد • تماسك • ترطيب • إشراقة</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>taglineFrench</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>✨ Le stick anti-ridules pour une peau visiblement plus lisse et plus ferme.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>descriptionFrench</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Sa formule aide à réduire l'apparence des rides et ridules, tout en apportant hydratation, confort et éclat à la peau.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>benefitsFrench</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Anti-ridules • Fermeté • Hydratation • Éclat</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>badgeArabic</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>مضاد للتجاعيد</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>freeShipping</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+          <t>📋 حالة الطلبات · Order Status</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="n"/>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>العدد</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="n"/>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C11" s="15">
+        <f>COUNTIF(Orders!C2:C,"New")</f>
+        <v/>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>جديد</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="n"/>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="C12" s="15">
+        <f>COUNTIF(Orders!C2:C,"Confirmed")</f>
+        <v/>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>مؤكد</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="C13" s="15">
+        <f>COUNTIF(Orders!C2:C,"Shipped")</f>
+        <v/>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>مشحون</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="C14" s="15">
+        <f>COUNTIF(Orders!C2:C,"Delivered")</f>
+        <v/>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>مسلّم</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="n"/>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="C15" s="15">
+        <f>COUNTIF(Orders!C2:C,"Cancelled")</f>
+        <v/>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>ملغى</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n"/>
+      <c r="F16" s="1" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>🌍 أعلى الولايات · Top Wilayas</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="n"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Wilaya</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Orders</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>الطلبات</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="19">
+        <f>IFERROR(INDEX(Orders!F2:F,MATCH(LARGE(IF(Orders!F2:F&lt;&gt;"",COUNTIF(Orders!F2:F,Orders!F2:F)),1),COUNTIF(Orders!F2:F,Orders!F2:F),0)),"")</f>
+        <v/>
+      </c>
+      <c r="C19" s="20">
+        <f>IFERROR(LARGE(IF(Orders!F2:F&lt;&gt;"",COUNTIF(Orders!F2:F,Orders!F2:F)),1),"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="19" t="inlineStr"/>
+      <c r="F19" s="1" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="19">
+        <f>IFERROR(INDEX(Orders!F2:F,MATCH(LARGE(IF(Orders!F2:F&lt;&gt;"",COUNTIF(Orders!F2:F,Orders!F2:F)),2),COUNTIF(Orders!F2:F,Orders!F2:F),0)),"")</f>
+        <v/>
+      </c>
+      <c r="C20" s="20">
+        <f>IFERROR(LARGE(IF(Orders!F2:F&lt;&gt;"",COUNTIF(Orders!F2:F,Orders!F2:F)),2),"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="19" t="inlineStr"/>
+      <c r="F20" s="1" t="n"/>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="19">
+        <f>IFERROR(INDEX(Orders!F2:F,MATCH(LARGE(IF(Orders!F2:F&lt;&gt;"",COUNTIF(Orders!F2:F,Orders!F2:F)),3),COUNTIF(Orders!F2:F,Orders!F2:F),0)),"")</f>
+        <v/>
+      </c>
+      <c r="C21" s="20">
+        <f>IFERROR(LARGE(IF(Orders!F2:F&lt;&gt;"",COUNTIF(Orders!F2:F,Orders!F2:F)),3),"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="19" t="inlineStr"/>
+      <c r="F21" s="1" t="n"/>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="19">
+        <f>IFERROR(INDEX(Orders!F2:F,MATCH(LARGE(IF(Orders!F2:F&lt;&gt;"",COUNTIF(Orders!F2:F,Orders!F2:F)),4),COUNTIF(Orders!F2:F,Orders!F2:F),0)),"")</f>
+        <v/>
+      </c>
+      <c r="C22" s="20">
+        <f>IFERROR(LARGE(IF(Orders!F2:F&lt;&gt;"",COUNTIF(Orders!F2:F,Orders!F2:F)),4),"")</f>
+        <v/>
+      </c>
+      <c r="D22" s="19" t="inlineStr"/>
+      <c r="F22" s="1" t="n"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="19">
+        <f>IFERROR(INDEX(Orders!F2:F,MATCH(LARGE(IF(Orders!F2:F&lt;&gt;"",COUNTIF(Orders!F2:F,Orders!F2:F)),5),COUNTIF(Orders!F2:F,Orders!F2:F),0)),"")</f>
+        <v/>
+      </c>
+      <c r="C23" s="20">
+        <f>IFERROR(LARGE(IF(Orders!F2:F&lt;&gt;"",COUNTIF(Orders!F2:F,Orders!F2:F)),5),"")</f>
+        <v/>
+      </c>
+      <c r="D23" s="19" t="inlineStr"/>
+      <c r="F23" s="1" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="F24" s="1" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>🕒 أحدث الطلبات · Recent Orders</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="n"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>Order No</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Wilaya</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>Total (DA)</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="19">
+        <f>IFERROR(INDEX(Orders!B2:B,COUNTA(Orders!B2:B)-0),"")</f>
+        <v/>
+      </c>
+      <c r="C27" s="19">
+        <f>IFERROR(INDEX(Orders!D2:D,COUNTA(Orders!D2:D)-0),"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="19">
+        <f>IFERROR(INDEX(Orders!F2:F,COUNTA(Orders!F2:F)-0),"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="20">
+        <f>IFERROR(INDEX(Orders!I2:I,COUNTA(Orders!I2:I)-0),"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="1" t="n"/>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="1" t="n"/>
+      <c r="B28" s="19">
+        <f>IFERROR(INDEX(Orders!B2:B,COUNTA(Orders!B2:B)-1),"")</f>
+        <v/>
+      </c>
+      <c r="C28" s="19">
+        <f>IFERROR(INDEX(Orders!D2:D,COUNTA(Orders!D2:D)-1),"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="19">
+        <f>IFERROR(INDEX(Orders!F2:F,COUNTA(Orders!F2:F)-1),"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="20">
+        <f>IFERROR(INDEX(Orders!I2:I,COUNTA(Orders!I2:I)-1),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="1" t="n"/>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="19">
+        <f>IFERROR(INDEX(Orders!B2:B,COUNTA(Orders!B2:B)-2),"")</f>
+        <v/>
+      </c>
+      <c r="C29" s="19">
+        <f>IFERROR(INDEX(Orders!D2:D,COUNTA(Orders!D2:D)-2),"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="19">
+        <f>IFERROR(INDEX(Orders!F2:F,COUNTA(Orders!F2:F)-2),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="20">
+        <f>IFERROR(INDEX(Orders!I2:I,COUNTA(Orders!I2:I)-2),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="1" t="n"/>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="19">
+        <f>IFERROR(INDEX(Orders!B2:B,COUNTA(Orders!B2:B)-3),"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="19">
+        <f>IFERROR(INDEX(Orders!D2:D,COUNTA(Orders!D2:D)-3),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="19">
+        <f>IFERROR(INDEX(Orders!F2:F,COUNTA(Orders!F2:F)-3),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="20">
+        <f>IFERROR(INDEX(Orders!I2:I,COUNTA(Orders!I2:I)-3),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="1" t="n"/>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="1" t="n"/>
+      <c r="B31" s="19">
+        <f>IFERROR(INDEX(Orders!B2:B,COUNTA(Orders!B2:B)-4),"")</f>
+        <v/>
+      </c>
+      <c r="C31" s="19">
+        <f>IFERROR(INDEX(Orders!D2:D,COUNTA(Orders!D2:D)-4),"")</f>
+        <v/>
+      </c>
+      <c r="D31" s="19">
+        <f>IFERROR(INDEX(Orders!F2:F,COUNTA(Orders!F2:F)-4),"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="20">
+        <f>IFERROR(INDEX(Orders!I2:I,COUNTA(Orders!I2:I)-4),"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="1" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n"/>
+      <c r="F32" s="1" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n"/>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>💡 يتم تحديث الإحصائيات تلقائياً عند كل طلب جديد</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n"/>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>💡 Statistics auto-update on every new order</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B34:E34"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -797,90 +1226,446 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Order No</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Wilaya</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Commune</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Total (DA)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>Idempotency Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="C2" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:K1"/>
   <conditionalFormatting sqref="C2:C5000">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
-      <formula>"New"</formula>
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$C2="New"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
-      <formula>"Confirmed"</formula>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>$C2="Confirmed"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
-      <formula>"Shipped"</formula>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>$C2="Shipped"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
-      <formula>"Delivered"</formula>
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>$C2="Delivered"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
-      <formula>"Cancelled"</formula>
+    <cfRule type="expression" priority="5" dxfId="4">
+      <formula>$C2="Cancelled"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -898,71 +1683,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>How it works</t>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>📦 Stock Management · إدارة المخزون</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Cemenrete CX</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>1. Set stock in B2 (e.g. 100)</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>2. Website checks this number</t>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>1. Set stock number in B2 (e.g. 100)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>3. Stock &lt;= 3: website shows warning</t>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>2. When you mark order 'Confirmed' → stock auto-reduces</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>4. Stock = 0: ordering disabled</t>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>3. Stock ≤ 3 → website shows 'low stock' warning</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>5. Change B2 anytime to restock</t>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>4. Stock = 0 → website disables ordering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>5. To restock → just change B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>💡 Stock auto-updates via trigger (onEditTrigger)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   when you change Status to 'Confirmed' in Orders tab</t>
         </is>
       </c>
     </row>
@@ -980,133 +1785,170 @@
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>Statistics</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>brandName</t>
+        </is>
+      </c>
+      <c r="B2" s="27" t="inlineStr">
+        <is>
+          <t>Dr.Melaxin</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>Total Orders</t>
-        </is>
-      </c>
-      <c r="B3" s="9">
-        <f>COUNTA(Orders!B2:B)</f>
-        <v/>
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>lineName</t>
+        </is>
+      </c>
+      <c r="B3" s="27" t="inlineStr">
+        <is>
+          <t>Cemenrete CX</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Total Revenue (DA)</t>
-        </is>
-      </c>
-      <c r="B4" s="9">
-        <f>SUM(Orders!I2:I)</f>
-        <v/>
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>Calcium Volume Multi Balm</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Avg Order (DA)</t>
-        </is>
-      </c>
-      <c r="B5" s="9">
-        <f>IFERROR(ROUND(AVERAGE(Orders!I2:I),0),0)</f>
-        <v/>
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>basePrice</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="n">
+        <v>3900</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Current Stock</t>
-        </is>
-      </c>
-      <c r="B6" s="9">
-        <f>Stock!B2</f>
-        <v/>
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>oldPrice</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="n">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>taglineArabic</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>✨ ستيك للعناية بالتجاعيد لبشرة أكثر نعومة وتماسكاً.</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>By Status</t>
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>descriptionArabic</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>تساعد تركيبته على تقليل مظهر التجاعيد والخطوط الدقيقة، مع ترطيب البشرة ومنحها مظهراً أكثر إشراقاً ونعومة.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>Count</t>
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>benefitsArabic</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>مضاد للتجاعيد • تماسك • ترطيب • إشراقة</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="B10" s="12">
-        <f>COUNTIF(Orders!C2:C,"New")</f>
-        <v/>
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>taglineFrench</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>✨ Le stick anti-ridules pour une peau visiblement plus lisse et plus ferme.</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="B11" s="12">
-        <f>COUNTIF(Orders!C2:C,"Confirmed")</f>
-        <v/>
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>descriptionFrench</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>Sa formule aide à réduire l'apparence des rides et ridules, tout en apportant hydratation, confort et éclat à la peau.</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="B12" s="12">
-        <f>COUNTIF(Orders!C2:C,"Shipped")</f>
-        <v/>
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>benefitsFrench</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>Anti-ridules • Fermeté • Hydratation • Éclat</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="B13" s="12">
-        <f>COUNTIF(Orders!C2:C,"Delivered")</f>
-        <v/>
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>badgeArabic</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>مضاد للتجاعيد</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>Cancelled</t>
-        </is>
-      </c>
-      <c r="B14" s="12">
-        <f>COUNTIF(Orders!C2:C,"Cancelled")</f>
-        <v/>
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>freeShipping</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/download/DrMelaxin-Sheet.xlsx
+++ b/download/DrMelaxin-Sheet.xlsx
@@ -989,66 +989,42 @@
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="19">
-        <f>IFERROR(INDEX(Orders!F2:F,MATCH(LARGE(IF(Orders!F2:F&lt;&gt;"",COUNTIF(Orders!F2:F,Orders!F2:F)),1),COUNTIF(Orders!F2:F,Orders!F2:F),0)),"")</f>
+        <f>IFERROR(QUERY(Orders!F2:F,"select F, count(F) where F is not null group by F order by count(F) desc limit 5 label count(F) ''",0),"")</f>
         <v/>
       </c>
       <c r="C19" s="20">
-        <f>IFERROR(LARGE(IF(Orders!F2:F&lt;&gt;"",COUNTIF(Orders!F2:F,Orders!F2:F)),1),"")</f>
+        <f>IFERROR(QUERY(Orders!F2:F,"select count(F) where F is not null group by F order by count(F) desc limit 5 label count(F) ''",0),"")</f>
         <v/>
       </c>
-      <c r="D19" s="19" t="inlineStr"/>
+      <c r="D19" s="19" t="n"/>
       <c r="F19" s="1" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="1" t="n"/>
-      <c r="B20" s="19">
-        <f>IFERROR(INDEX(Orders!F2:F,MATCH(LARGE(IF(Orders!F2:F&lt;&gt;"",COUNTIF(Orders!F2:F,Orders!F2:F)),2),COUNTIF(Orders!F2:F,Orders!F2:F),0)),"")</f>
-        <v/>
-      </c>
-      <c r="C20" s="20">
-        <f>IFERROR(LARGE(IF(Orders!F2:F&lt;&gt;"",COUNTIF(Orders!F2:F,Orders!F2:F)),2),"")</f>
-        <v/>
-      </c>
-      <c r="D20" s="19" t="inlineStr"/>
+      <c r="B20" s="19" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="19" t="n"/>
       <c r="F20" s="1" t="n"/>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="1" t="n"/>
-      <c r="B21" s="19">
-        <f>IFERROR(INDEX(Orders!F2:F,MATCH(LARGE(IF(Orders!F2:F&lt;&gt;"",COUNTIF(Orders!F2:F,Orders!F2:F)),3),COUNTIF(Orders!F2:F,Orders!F2:F),0)),"")</f>
-        <v/>
-      </c>
-      <c r="C21" s="20">
-        <f>IFERROR(LARGE(IF(Orders!F2:F&lt;&gt;"",COUNTIF(Orders!F2:F,Orders!F2:F)),3),"")</f>
-        <v/>
-      </c>
-      <c r="D21" s="19" t="inlineStr"/>
+      <c r="B21" s="19" t="n"/>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="19" t="n"/>
       <c r="F21" s="1" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="1" t="n"/>
-      <c r="B22" s="19">
-        <f>IFERROR(INDEX(Orders!F2:F,MATCH(LARGE(IF(Orders!F2:F&lt;&gt;"",COUNTIF(Orders!F2:F,Orders!F2:F)),4),COUNTIF(Orders!F2:F,Orders!F2:F),0)),"")</f>
-        <v/>
-      </c>
-      <c r="C22" s="20">
-        <f>IFERROR(LARGE(IF(Orders!F2:F&lt;&gt;"",COUNTIF(Orders!F2:F,Orders!F2:F)),4),"")</f>
-        <v/>
-      </c>
-      <c r="D22" s="19" t="inlineStr"/>
+      <c r="B22" s="19" t="n"/>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="19" t="n"/>
       <c r="F22" s="1" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="1" t="n"/>
-      <c r="B23" s="19">
-        <f>IFERROR(INDEX(Orders!F2:F,MATCH(LARGE(IF(Orders!F2:F&lt;&gt;"",COUNTIF(Orders!F2:F,Orders!F2:F)),5),COUNTIF(Orders!F2:F,Orders!F2:F),0)),"")</f>
-        <v/>
-      </c>
-      <c r="C23" s="20">
-        <f>IFERROR(LARGE(IF(Orders!F2:F&lt;&gt;"",COUNTIF(Orders!F2:F,Orders!F2:F)),5),"")</f>
-        <v/>
-      </c>
-      <c r="D23" s="19" t="inlineStr"/>
+      <c r="B23" s="19" t="n"/>
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="19" t="n"/>
       <c r="F23" s="1" t="n"/>
     </row>
     <row r="24">
@@ -1091,101 +1067,44 @@
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="19">
-        <f>IFERROR(INDEX(Orders!B2:B,COUNTA(Orders!B2:B)-0),"")</f>
+        <f>IFERROR(QUERY(Orders!B2:I,"select B, D, F, I order by A desc limit 5 label B '', D '', F '', I ''",0),"")</f>
         <v/>
       </c>
-      <c r="C27" s="19">
-        <f>IFERROR(INDEX(Orders!D2:D,COUNTA(Orders!D2:D)-0),"")</f>
-        <v/>
-      </c>
-      <c r="D27" s="19">
-        <f>IFERROR(INDEX(Orders!F2:F,COUNTA(Orders!F2:F)-0),"")</f>
-        <v/>
-      </c>
-      <c r="E27" s="20">
-        <f>IFERROR(INDEX(Orders!I2:I,COUNTA(Orders!I2:I)-0),"")</f>
-        <v/>
-      </c>
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="20" t="n"/>
       <c r="F27" s="1" t="n"/>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="1" t="n"/>
-      <c r="B28" s="19">
-        <f>IFERROR(INDEX(Orders!B2:B,COUNTA(Orders!B2:B)-1),"")</f>
-        <v/>
-      </c>
-      <c r="C28" s="19">
-        <f>IFERROR(INDEX(Orders!D2:D,COUNTA(Orders!D2:D)-1),"")</f>
-        <v/>
-      </c>
-      <c r="D28" s="19">
-        <f>IFERROR(INDEX(Orders!F2:F,COUNTA(Orders!F2:F)-1),"")</f>
-        <v/>
-      </c>
-      <c r="E28" s="20">
-        <f>IFERROR(INDEX(Orders!I2:I,COUNTA(Orders!I2:I)-1),"")</f>
-        <v/>
-      </c>
+      <c r="B28" s="19" t="n"/>
+      <c r="C28" s="19" t="n"/>
+      <c r="D28" s="19" t="n"/>
+      <c r="E28" s="20" t="n"/>
       <c r="F28" s="1" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="1" t="n"/>
-      <c r="B29" s="19">
-        <f>IFERROR(INDEX(Orders!B2:B,COUNTA(Orders!B2:B)-2),"")</f>
-        <v/>
-      </c>
-      <c r="C29" s="19">
-        <f>IFERROR(INDEX(Orders!D2:D,COUNTA(Orders!D2:D)-2),"")</f>
-        <v/>
-      </c>
-      <c r="D29" s="19">
-        <f>IFERROR(INDEX(Orders!F2:F,COUNTA(Orders!F2:F)-2),"")</f>
-        <v/>
-      </c>
-      <c r="E29" s="20">
-        <f>IFERROR(INDEX(Orders!I2:I,COUNTA(Orders!I2:I)-2),"")</f>
-        <v/>
-      </c>
+      <c r="B29" s="19" t="n"/>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="20" t="n"/>
       <c r="F29" s="1" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="1" t="n"/>
-      <c r="B30" s="19">
-        <f>IFERROR(INDEX(Orders!B2:B,COUNTA(Orders!B2:B)-3),"")</f>
-        <v/>
-      </c>
-      <c r="C30" s="19">
-        <f>IFERROR(INDEX(Orders!D2:D,COUNTA(Orders!D2:D)-3),"")</f>
-        <v/>
-      </c>
-      <c r="D30" s="19">
-        <f>IFERROR(INDEX(Orders!F2:F,COUNTA(Orders!F2:F)-3),"")</f>
-        <v/>
-      </c>
-      <c r="E30" s="20">
-        <f>IFERROR(INDEX(Orders!I2:I,COUNTA(Orders!I2:I)-3),"")</f>
-        <v/>
-      </c>
+      <c r="B30" s="19" t="n"/>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="20" t="n"/>
       <c r="F30" s="1" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="1" t="n"/>
-      <c r="B31" s="19">
-        <f>IFERROR(INDEX(Orders!B2:B,COUNTA(Orders!B2:B)-4),"")</f>
-        <v/>
-      </c>
-      <c r="C31" s="19">
-        <f>IFERROR(INDEX(Orders!D2:D,COUNTA(Orders!D2:D)-4),"")</f>
-        <v/>
-      </c>
-      <c r="D31" s="19">
-        <f>IFERROR(INDEX(Orders!F2:F,COUNTA(Orders!F2:F)-4),"")</f>
-        <v/>
-      </c>
-      <c r="E31" s="20">
-        <f>IFERROR(INDEX(Orders!I2:I,COUNTA(Orders!I2:I)-4),"")</f>
-        <v/>
-      </c>
+      <c r="B31" s="19" t="n"/>
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="20" t="n"/>
       <c r="F31" s="1" t="n"/>
     </row>
     <row r="32">

--- a/download/DrMelaxin-Sheet.xlsx
+++ b/download/DrMelaxin-Sheet.xlsx
@@ -989,13 +989,10 @@
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="19">
-        <f>IFERROR(QUERY(Orders!F2:F,"select F, count(F) where F is not null group by F order by count(F) desc limit 5 label count(F) ''",0),"")</f>
+        <f>IFERROR(QUERY(Orders!F2:I,"select F, count(F) where F is not null and F != '' group by F order by count(F) desc limit 5 label F 'Wilaya', count(F) 'Orders'",0),"No orders yet")</f>
         <v/>
       </c>
-      <c r="C19" s="20">
-        <f>IFERROR(QUERY(Orders!F2:F,"select count(F) where F is not null group by F order by count(F) desc limit 5 label count(F) ''",0),"")</f>
-        <v/>
-      </c>
+      <c r="C19" s="20" t="n"/>
       <c r="D19" s="19" t="n"/>
       <c r="F19" s="1" t="n"/>
     </row>
@@ -1067,7 +1064,7 @@
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="19">
-        <f>IFERROR(QUERY(Orders!B2:I,"select B, D, F, I order by A desc limit 5 label B '', D '', F '', I ''",0),"")</f>
+        <f>IFERROR(QUERY(Orders!B2:I,"select B, D, F, I where B is not null order by A desc limit 5 label B '', D '', F '', I ''",0),"No orders yet")</f>
         <v/>
       </c>
       <c r="C27" s="19" t="n"/>
